--- a/docs/downloads/Metatya-Trading-Journal-LITE.xlsx
+++ b/docs/downloads/Metatya-Trading-Journal-LITE.xlsx
@@ -13,6 +13,7 @@
     <sheet name="محاسبه حجم" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="چک‌لیست قبل از معامله" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="دفترچه معاملات" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="پرتفوی بورس" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="104">
   <si>
     <t xml:space="preserve">Metatya | دفترچه معاملات و مدیریت ریسک (نسخه‌ی رایگان)</t>
   </si>
@@ -53,6 +54,9 @@
     <t xml:space="preserve">R-multiple یعنی سود/زیان را بر ریسک اولیه‌ی همان معامله تقسیم کنیم؛ +2R یعنی دو برابر ریسک سود کرده‌اید.</t>
   </si>
   <si>
+    <t xml:space="preserve">برگه‌ی «پرتفوی بورس»: نماد، تعداد، میانگین خرید و قیمت روز را بنویس؛ ارزش خالص (بعد از کارمزد فروش)، سود/زیان، وزن هر نماد و هشدار تمرکز خودکار حساب می‌شود.</t>
+  </si>
+  <si>
     <t xml:space="preserve">سلب مسئولیت: این فایل ابزار ثبت و آموزش است؛ توصیه‌ی سرمایه‌گذاری یا وعده‌ی سود نیست. معامله‌ی بازارهای مالی ریسک زیان دارد.</t>
   </si>
   <si>
@@ -261,13 +265,85 @@
   </si>
   <si>
     <t xml:space="preserve">نمونه: شکست حمایت ۱٫۱۳۱۲ و ورود در پولبک</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ردیاب پرتفوی بورس (ریال)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کارمزد و مالیات فروش (٪ از ارزش)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">در نمونه‌ی اپ کارگزاری مرجع، «ارزش فعلی» حدود ۰٫۸۸٪ کمتر از تعداد×قیمت بود؛ نرخ کارگزاری خودت را بنویس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قدرت خرید (ریال)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">از اپ کارگزاری بردار؛ عدد نمونه است</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حداکثر وزن مجاز هر نماد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بالاتر از این عدد هشدار تمرکز می‌دهد (قانون خودت را بنویس)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تعداد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">میانگین قیمت خرید</t>
+  </si>
+  <si>
+    <t xml:space="preserve">آخرین قیمت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قیمت پایانی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ارزش فعلی (خالص)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هزینه‌ی کل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سود/زیان ٪</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تغییر امروز ٪</t>
+  </si>
+  <si>
+    <t xml:space="preserve">وزن در پرتفوی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هشدار</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نمونه ۱</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نمونه ۲</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نمونه ۳</t>
+  </si>
+  <si>
+    <t xml:space="preserve">جمع پرتفوی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کل دارایی (پرتفوی + قدرت خرید)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بزرگ‌ترین وزن یک نماد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قیمت‌ها را خودت از اپ کارگزاری بنویس (این فایل به بورس وصل نیست). ردیف‌های «نمونه» را پاک کن. آموزشی است و توصیه‌ی خرید/فروش یا سرمایه‌گذاری نیست.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="15">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%;\-0.0%;\-"/>
@@ -277,8 +353,14 @@
     <numFmt numFmtId="170" formatCode="0.00"/>
     <numFmt numFmtId="171" formatCode="#,##0.00"/>
     <numFmt numFmtId="172" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="173" formatCode="0.00%"/>
+    <numFmt numFmtId="174" formatCode="#,##0"/>
+    <numFmt numFmtId="175" formatCode="0%"/>
+    <numFmt numFmtId="176" formatCode="#,##0;[RED]\-#,##0"/>
+    <numFmt numFmtId="177" formatCode="0.0%;[RED]\-0.0%"/>
+    <numFmt numFmtId="178" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -358,6 +440,13 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF666666"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -428,7 +517,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="43">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -542,6 +631,62 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="175" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -797,7 +942,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="1" style="0" width="20"/>
@@ -903,7 +1048,7 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
     </row>
-    <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
@@ -913,8 +1058,18 @@
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
     </row>
+    <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A4:F4"/>
@@ -926,6 +1081,7 @@
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A13:F13"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -952,75 +1108,75 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" s="6" t="n">
         <v>10000</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B5" s="8" t="n">
         <v>0.01</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6" s="8" t="n">
         <v>0.05</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7" s="9" t="n">
         <v>1.5</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1052,25 +1208,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B4" s="12" t="n">
         <v>1.128</v>
@@ -1079,18 +1235,18 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5" s="12" t="n">
         <v>1.133</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6" s="12" t="n">
         <v>1.118</v>
@@ -1099,53 +1255,53 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B7" s="14" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B10" s="15" t="n">
         <f aca="false">تنظیمات!$B$4+SUM('دفترچه معاملات'!$K$5:$K$24)</f>
         <v>10070</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B11" s="15" t="n">
         <f aca="false">B10*تنظیمات!$B$5</f>
         <v>100.7</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12" s="16" t="n">
         <f aca="false">ABS(B4-B5)</f>
@@ -1155,19 +1311,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13" s="18" t="n">
         <f aca="false">IF(OR(B12=0,B7=0),"",B11/(B12*B7))</f>
         <v>20139.9999999995</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14" s="19" t="n">
         <f aca="false">IF(B12=0,"",ABS(B6-B4)/B12)</f>
@@ -1177,7 +1333,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B15" s="15" t="n">
         <f aca="false">IF(B13="","",B13*ABS(B6-B4)*B7)</f>
@@ -1187,7 +1343,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16" s="20" t="str">
         <f aca="false">IF(B14="","ورودی را کامل کنید",IF(B14&gt;=تنظیمات!$B$7,"✅ R:R قابل قبول","❌ R:R کمتر از حداقل؛ وارد نشوید"))</f>
@@ -1224,73 +1380,73 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B4" s="21"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B5" s="21"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B6" s="21"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B7" s="21"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B8" s="21"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B9" s="21"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B10" s="21"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B11" s="21"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B13" s="22" t="str">
         <f aca="false">IF(COUNTIF(B4:B11,"بله")=8,"✅ مجاز به ورود","⛔ هنوز نه")</f>
@@ -1299,7 +1455,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1348,7 +1504,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1370,7 +1526,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="23" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B2" s="23"/>
       <c r="C2" s="23"/>
@@ -1392,58 +1548,58 @@
     </row>
     <row r="4" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1454,10 +1610,10 @@
         <v>46297</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>1.128</v>
@@ -1490,13 +1646,13 @@
         <v>برد</v>
       </c>
       <c r="N5" s="21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O5" s="21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P5" s="27" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q5" s="15" t="n">
         <f aca="false">IF(K5="","",تنظیمات!$B$4+SUM(K$5:K5))</f>
@@ -2237,4 +2393,777 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:L26"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="30" t="n">
+        <v>0.0088</v>
+      </c>
+      <c r="E2" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="32" t="n">
+        <v>19899409</v>
+      </c>
+      <c r="E3" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="33" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+    </row>
+    <row r="5" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="B6" s="32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C6" s="32" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D6" s="32" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E6" s="32" t="n">
+        <v>11900</v>
+      </c>
+      <c r="F6" s="34" t="n">
+        <f aca="false">IF(OR(B6="",D6=""),"",B6*D6*(1-$D$2))</f>
+        <v>11894400</v>
+      </c>
+      <c r="G6" s="34" t="n">
+        <f aca="false">IF(OR(B6="",C6=""),"",B6*C6)</f>
+        <v>10000000</v>
+      </c>
+      <c r="H6" s="35" t="n">
+        <f aca="false">IF(OR(F6="",G6=""),"",F6-G6)</f>
+        <v>1894400</v>
+      </c>
+      <c r="I6" s="36" t="n">
+        <f aca="false">IF(OR(H6="",G6="",G6=0),"",H6/G6)</f>
+        <v>0.18944</v>
+      </c>
+      <c r="J6" s="36" t="n">
+        <f aca="false">IF(OR(D6="",E6="",E6=0),"",D6/E6-1)</f>
+        <v>0.00840336134453779</v>
+      </c>
+      <c r="K6" s="37" t="n">
+        <f aca="false">IF(OR(F6="",$F$22=0),"",F6/$F$22)</f>
+        <v>0.292682926829268</v>
+      </c>
+      <c r="L6" s="26" t="str">
+        <f aca="false">IF(K6="","",IF(K6&gt;$D$4,"⚠️ تمرکز بالا",""))</f>
+        <v>⚠️ تمرکز بالا</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" s="32" t="n">
+        <v>500</v>
+      </c>
+      <c r="C7" s="32" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D7" s="32" t="n">
+        <v>22000</v>
+      </c>
+      <c r="E7" s="32" t="n">
+        <v>22500</v>
+      </c>
+      <c r="F7" s="34" t="n">
+        <f aca="false">IF(OR(B7="",D7=""),"",B7*D7*(1-$D$2))</f>
+        <v>10903200</v>
+      </c>
+      <c r="G7" s="34" t="n">
+        <f aca="false">IF(OR(B7="",C7=""),"",B7*C7)</f>
+        <v>12500000</v>
+      </c>
+      <c r="H7" s="35" t="n">
+        <f aca="false">IF(OR(F7="",G7=""),"",F7-G7)</f>
+        <v>-1596800</v>
+      </c>
+      <c r="I7" s="36" t="n">
+        <f aca="false">IF(OR(H7="",G7="",G7=0),"",H7/G7)</f>
+        <v>-0.127744</v>
+      </c>
+      <c r="J7" s="36" t="n">
+        <f aca="false">IF(OR(D7="",E7="",E7=0),"",D7/E7-1)</f>
+        <v>-0.0222222222222223</v>
+      </c>
+      <c r="K7" s="37" t="n">
+        <f aca="false">IF(OR(F7="",$F$22=0),"",F7/$F$22)</f>
+        <v>0.268292682926829</v>
+      </c>
+      <c r="L7" s="26" t="str">
+        <f aca="false">IF(K7="","",IF(K7&gt;$D$4,"⚠️ تمرکز بالا",""))</f>
+        <v>⚠️ تمرکز بالا</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="B8" s="32" t="n">
+        <v>200</v>
+      </c>
+      <c r="C8" s="32" t="n">
+        <v>80000</v>
+      </c>
+      <c r="D8" s="32" t="n">
+        <v>90000</v>
+      </c>
+      <c r="E8" s="32" t="n">
+        <v>90000</v>
+      </c>
+      <c r="F8" s="34" t="n">
+        <f aca="false">IF(OR(B8="",D8=""),"",B8*D8*(1-$D$2))</f>
+        <v>17841600</v>
+      </c>
+      <c r="G8" s="34" t="n">
+        <f aca="false">IF(OR(B8="",C8=""),"",B8*C8)</f>
+        <v>16000000</v>
+      </c>
+      <c r="H8" s="35" t="n">
+        <f aca="false">IF(OR(F8="",G8=""),"",F8-G8)</f>
+        <v>1841600</v>
+      </c>
+      <c r="I8" s="36" t="n">
+        <f aca="false">IF(OR(H8="",G8="",G8=0),"",H8/G8)</f>
+        <v>0.1151</v>
+      </c>
+      <c r="J8" s="36" t="n">
+        <f aca="false">IF(OR(D8="",E8="",E8=0),"",D8/E8-1)</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="37" t="n">
+        <f aca="false">IF(OR(F8="",$F$22=0),"",F8/$F$22)</f>
+        <v>0.439024390243902</v>
+      </c>
+      <c r="L8" s="26" t="str">
+        <f aca="false">IF(K8="","",IF(K8&gt;$D$4,"⚠️ تمرکز بالا",""))</f>
+        <v>⚠️ تمرکز بالا</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="21"/>
+      <c r="B9" s="32"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="34" t="str">
+        <f aca="false">IF(OR(B9="",D9=""),"",B9*D9*(1-$D$2))</f>
+        <v/>
+      </c>
+      <c r="G9" s="34" t="str">
+        <f aca="false">IF(OR(B9="",C9=""),"",B9*C9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="35" t="str">
+        <f aca="false">IF(OR(F9="",G9=""),"",F9-G9)</f>
+        <v/>
+      </c>
+      <c r="I9" s="36" t="str">
+        <f aca="false">IF(OR(H9="",G9="",G9=0),"",H9/G9)</f>
+        <v/>
+      </c>
+      <c r="J9" s="36" t="str">
+        <f aca="false">IF(OR(D9="",E9="",E9=0),"",D9/E9-1)</f>
+        <v/>
+      </c>
+      <c r="K9" s="37" t="str">
+        <f aca="false">IF(OR(F9="",$F$22=0),"",F9/$F$22)</f>
+        <v/>
+      </c>
+      <c r="L9" s="26" t="str">
+        <f aca="false">IF(K9="","",IF(K9&gt;$D$4,"⚠️ تمرکز بالا",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="21"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="34" t="str">
+        <f aca="false">IF(OR(B10="",D10=""),"",B10*D10*(1-$D$2))</f>
+        <v/>
+      </c>
+      <c r="G10" s="34" t="str">
+        <f aca="false">IF(OR(B10="",C10=""),"",B10*C10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="35" t="str">
+        <f aca="false">IF(OR(F10="",G10=""),"",F10-G10)</f>
+        <v/>
+      </c>
+      <c r="I10" s="36" t="str">
+        <f aca="false">IF(OR(H10="",G10="",G10=0),"",H10/G10)</f>
+        <v/>
+      </c>
+      <c r="J10" s="36" t="str">
+        <f aca="false">IF(OR(D10="",E10="",E10=0),"",D10/E10-1)</f>
+        <v/>
+      </c>
+      <c r="K10" s="37" t="str">
+        <f aca="false">IF(OR(F10="",$F$22=0),"",F10/$F$22)</f>
+        <v/>
+      </c>
+      <c r="L10" s="26" t="str">
+        <f aca="false">IF(K10="","",IF(K10&gt;$D$4,"⚠️ تمرکز بالا",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="21"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="34" t="str">
+        <f aca="false">IF(OR(B11="",D11=""),"",B11*D11*(1-$D$2))</f>
+        <v/>
+      </c>
+      <c r="G11" s="34" t="str">
+        <f aca="false">IF(OR(B11="",C11=""),"",B11*C11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="35" t="str">
+        <f aca="false">IF(OR(F11="",G11=""),"",F11-G11)</f>
+        <v/>
+      </c>
+      <c r="I11" s="36" t="str">
+        <f aca="false">IF(OR(H11="",G11="",G11=0),"",H11/G11)</f>
+        <v/>
+      </c>
+      <c r="J11" s="36" t="str">
+        <f aca="false">IF(OR(D11="",E11="",E11=0),"",D11/E11-1)</f>
+        <v/>
+      </c>
+      <c r="K11" s="37" t="str">
+        <f aca="false">IF(OR(F11="",$F$22=0),"",F11/$F$22)</f>
+        <v/>
+      </c>
+      <c r="L11" s="26" t="str">
+        <f aca="false">IF(K11="","",IF(K11&gt;$D$4,"⚠️ تمرکز بالا",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="21"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="34" t="str">
+        <f aca="false">IF(OR(B12="",D12=""),"",B12*D12*(1-$D$2))</f>
+        <v/>
+      </c>
+      <c r="G12" s="34" t="str">
+        <f aca="false">IF(OR(B12="",C12=""),"",B12*C12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="35" t="str">
+        <f aca="false">IF(OR(F12="",G12=""),"",F12-G12)</f>
+        <v/>
+      </c>
+      <c r="I12" s="36" t="str">
+        <f aca="false">IF(OR(H12="",G12="",G12=0),"",H12/G12)</f>
+        <v/>
+      </c>
+      <c r="J12" s="36" t="str">
+        <f aca="false">IF(OR(D12="",E12="",E12=0),"",D12/E12-1)</f>
+        <v/>
+      </c>
+      <c r="K12" s="37" t="str">
+        <f aca="false">IF(OR(F12="",$F$22=0),"",F12/$F$22)</f>
+        <v/>
+      </c>
+      <c r="L12" s="26" t="str">
+        <f aca="false">IF(K12="","",IF(K12&gt;$D$4,"⚠️ تمرکز بالا",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="21"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="34" t="str">
+        <f aca="false">IF(OR(B13="",D13=""),"",B13*D13*(1-$D$2))</f>
+        <v/>
+      </c>
+      <c r="G13" s="34" t="str">
+        <f aca="false">IF(OR(B13="",C13=""),"",B13*C13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="35" t="str">
+        <f aca="false">IF(OR(F13="",G13=""),"",F13-G13)</f>
+        <v/>
+      </c>
+      <c r="I13" s="36" t="str">
+        <f aca="false">IF(OR(H13="",G13="",G13=0),"",H13/G13)</f>
+        <v/>
+      </c>
+      <c r="J13" s="36" t="str">
+        <f aca="false">IF(OR(D13="",E13="",E13=0),"",D13/E13-1)</f>
+        <v/>
+      </c>
+      <c r="K13" s="37" t="str">
+        <f aca="false">IF(OR(F13="",$F$22=0),"",F13/$F$22)</f>
+        <v/>
+      </c>
+      <c r="L13" s="26" t="str">
+        <f aca="false">IF(K13="","",IF(K13&gt;$D$4,"⚠️ تمرکز بالا",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="21"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="34" t="str">
+        <f aca="false">IF(OR(B14="",D14=""),"",B14*D14*(1-$D$2))</f>
+        <v/>
+      </c>
+      <c r="G14" s="34" t="str">
+        <f aca="false">IF(OR(B14="",C14=""),"",B14*C14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="35" t="str">
+        <f aca="false">IF(OR(F14="",G14=""),"",F14-G14)</f>
+        <v/>
+      </c>
+      <c r="I14" s="36" t="str">
+        <f aca="false">IF(OR(H14="",G14="",G14=0),"",H14/G14)</f>
+        <v/>
+      </c>
+      <c r="J14" s="36" t="str">
+        <f aca="false">IF(OR(D14="",E14="",E14=0),"",D14/E14-1)</f>
+        <v/>
+      </c>
+      <c r="K14" s="37" t="str">
+        <f aca="false">IF(OR(F14="",$F$22=0),"",F14/$F$22)</f>
+        <v/>
+      </c>
+      <c r="L14" s="26" t="str">
+        <f aca="false">IF(K14="","",IF(K14&gt;$D$4,"⚠️ تمرکز بالا",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="21"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="34" t="str">
+        <f aca="false">IF(OR(B15="",D15=""),"",B15*D15*(1-$D$2))</f>
+        <v/>
+      </c>
+      <c r="G15" s="34" t="str">
+        <f aca="false">IF(OR(B15="",C15=""),"",B15*C15)</f>
+        <v/>
+      </c>
+      <c r="H15" s="35" t="str">
+        <f aca="false">IF(OR(F15="",G15=""),"",F15-G15)</f>
+        <v/>
+      </c>
+      <c r="I15" s="36" t="str">
+        <f aca="false">IF(OR(H15="",G15="",G15=0),"",H15/G15)</f>
+        <v/>
+      </c>
+      <c r="J15" s="36" t="str">
+        <f aca="false">IF(OR(D15="",E15="",E15=0),"",D15/E15-1)</f>
+        <v/>
+      </c>
+      <c r="K15" s="37" t="str">
+        <f aca="false">IF(OR(F15="",$F$22=0),"",F15/$F$22)</f>
+        <v/>
+      </c>
+      <c r="L15" s="26" t="str">
+        <f aca="false">IF(K15="","",IF(K15&gt;$D$4,"⚠️ تمرکز بالا",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="21"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="34" t="str">
+        <f aca="false">IF(OR(B16="",D16=""),"",B16*D16*(1-$D$2))</f>
+        <v/>
+      </c>
+      <c r="G16" s="34" t="str">
+        <f aca="false">IF(OR(B16="",C16=""),"",B16*C16)</f>
+        <v/>
+      </c>
+      <c r="H16" s="35" t="str">
+        <f aca="false">IF(OR(F16="",G16=""),"",F16-G16)</f>
+        <v/>
+      </c>
+      <c r="I16" s="36" t="str">
+        <f aca="false">IF(OR(H16="",G16="",G16=0),"",H16/G16)</f>
+        <v/>
+      </c>
+      <c r="J16" s="36" t="str">
+        <f aca="false">IF(OR(D16="",E16="",E16=0),"",D16/E16-1)</f>
+        <v/>
+      </c>
+      <c r="K16" s="37" t="str">
+        <f aca="false">IF(OR(F16="",$F$22=0),"",F16/$F$22)</f>
+        <v/>
+      </c>
+      <c r="L16" s="26" t="str">
+        <f aca="false">IF(K16="","",IF(K16&gt;$D$4,"⚠️ تمرکز بالا",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="21"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="34" t="str">
+        <f aca="false">IF(OR(B17="",D17=""),"",B17*D17*(1-$D$2))</f>
+        <v/>
+      </c>
+      <c r="G17" s="34" t="str">
+        <f aca="false">IF(OR(B17="",C17=""),"",B17*C17)</f>
+        <v/>
+      </c>
+      <c r="H17" s="35" t="str">
+        <f aca="false">IF(OR(F17="",G17=""),"",F17-G17)</f>
+        <v/>
+      </c>
+      <c r="I17" s="36" t="str">
+        <f aca="false">IF(OR(H17="",G17="",G17=0),"",H17/G17)</f>
+        <v/>
+      </c>
+      <c r="J17" s="36" t="str">
+        <f aca="false">IF(OR(D17="",E17="",E17=0),"",D17/E17-1)</f>
+        <v/>
+      </c>
+      <c r="K17" s="37" t="str">
+        <f aca="false">IF(OR(F17="",$F$22=0),"",F17/$F$22)</f>
+        <v/>
+      </c>
+      <c r="L17" s="26" t="str">
+        <f aca="false">IF(K17="","",IF(K17&gt;$D$4,"⚠️ تمرکز بالا",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="21"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="34" t="str">
+        <f aca="false">IF(OR(B18="",D18=""),"",B18*D18*(1-$D$2))</f>
+        <v/>
+      </c>
+      <c r="G18" s="34" t="str">
+        <f aca="false">IF(OR(B18="",C18=""),"",B18*C18)</f>
+        <v/>
+      </c>
+      <c r="H18" s="35" t="str">
+        <f aca="false">IF(OR(F18="",G18=""),"",F18-G18)</f>
+        <v/>
+      </c>
+      <c r="I18" s="36" t="str">
+        <f aca="false">IF(OR(H18="",G18="",G18=0),"",H18/G18)</f>
+        <v/>
+      </c>
+      <c r="J18" s="36" t="str">
+        <f aca="false">IF(OR(D18="",E18="",E18=0),"",D18/E18-1)</f>
+        <v/>
+      </c>
+      <c r="K18" s="37" t="str">
+        <f aca="false">IF(OR(F18="",$F$22=0),"",F18/$F$22)</f>
+        <v/>
+      </c>
+      <c r="L18" s="26" t="str">
+        <f aca="false">IF(K18="","",IF(K18&gt;$D$4,"⚠️ تمرکز بالا",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="21"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="34" t="str">
+        <f aca="false">IF(OR(B19="",D19=""),"",B19*D19*(1-$D$2))</f>
+        <v/>
+      </c>
+      <c r="G19" s="34" t="str">
+        <f aca="false">IF(OR(B19="",C19=""),"",B19*C19)</f>
+        <v/>
+      </c>
+      <c r="H19" s="35" t="str">
+        <f aca="false">IF(OR(F19="",G19=""),"",F19-G19)</f>
+        <v/>
+      </c>
+      <c r="I19" s="36" t="str">
+        <f aca="false">IF(OR(H19="",G19="",G19=0),"",H19/G19)</f>
+        <v/>
+      </c>
+      <c r="J19" s="36" t="str">
+        <f aca="false">IF(OR(D19="",E19="",E19=0),"",D19/E19-1)</f>
+        <v/>
+      </c>
+      <c r="K19" s="37" t="str">
+        <f aca="false">IF(OR(F19="",$F$22=0),"",F19/$F$22)</f>
+        <v/>
+      </c>
+      <c r="L19" s="26" t="str">
+        <f aca="false">IF(K19="","",IF(K19&gt;$D$4,"⚠️ تمرکز بالا",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="21"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="34" t="str">
+        <f aca="false">IF(OR(B20="",D20=""),"",B20*D20*(1-$D$2))</f>
+        <v/>
+      </c>
+      <c r="G20" s="34" t="str">
+        <f aca="false">IF(OR(B20="",C20=""),"",B20*C20)</f>
+        <v/>
+      </c>
+      <c r="H20" s="35" t="str">
+        <f aca="false">IF(OR(F20="",G20=""),"",F20-G20)</f>
+        <v/>
+      </c>
+      <c r="I20" s="36" t="str">
+        <f aca="false">IF(OR(H20="",G20="",G20=0),"",H20/G20)</f>
+        <v/>
+      </c>
+      <c r="J20" s="36" t="str">
+        <f aca="false">IF(OR(D20="",E20="",E20=0),"",D20/E20-1)</f>
+        <v/>
+      </c>
+      <c r="K20" s="37" t="str">
+        <f aca="false">IF(OR(F20="",$F$22=0),"",F20/$F$22)</f>
+        <v/>
+      </c>
+      <c r="L20" s="26" t="str">
+        <f aca="false">IF(K20="","",IF(K20&gt;$D$4,"⚠️ تمرکز بالا",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="F22" s="38" t="n">
+        <f aca="false">SUM(F6:F20)</f>
+        <v>40639200</v>
+      </c>
+      <c r="G22" s="38" t="n">
+        <f aca="false">SUM(G6:G20)</f>
+        <v>38500000</v>
+      </c>
+      <c r="H22" s="39" t="n">
+        <f aca="false">SUM(H6:H20)</f>
+        <v>2139200</v>
+      </c>
+      <c r="I22" s="40" t="n">
+        <f aca="false">IF(G22=0,"",H22/G22)</f>
+        <v>0.0555636363636364</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="B23" s="41"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="38" t="n">
+        <f aca="false">F22+D3</f>
+        <v>60538609</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="41"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="42" t="n">
+        <f aca="false">IF(COUNT(K6:K20)=0,"",MAX(K6:K20))</f>
+        <v>0.439024390243902</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="B26" s="31"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="E2:L2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="E3:L3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="E4:L4"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A26:L26"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>